--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N107_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N107_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.26684371055955</v>
+        <v>7.355862102965927</v>
       </c>
       <c r="D2" t="n">
-        <v>18.89414785436669</v>
+        <v>3.070299026334586</v>
       </c>
       <c r="E2" t="n">
-        <v>6.572989155237063</v>
+        <v>1.068110737726023</v>
       </c>
       <c r="F2" t="n">
-        <v>7.743592024567654</v>
+        <v>1.258333703992244</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.11059592569153</v>
+        <v>4.567971837924874</v>
       </c>
       <c r="D3" t="n">
-        <v>26.7445800233515</v>
+        <v>4.345994253794618</v>
       </c>
       <c r="E3" t="n">
-        <v>6.572989155237063</v>
+        <v>1.068110737726023</v>
       </c>
       <c r="F3" t="n">
-        <v>7.743592024567654</v>
+        <v>1.258333703992244</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.89016620906197</v>
+        <v>6.80715200897257</v>
       </c>
       <c r="D4" t="n">
-        <v>41.48673548902549</v>
+        <v>6.741594516966643</v>
       </c>
       <c r="E4" t="n">
-        <v>6.572989155237063</v>
+        <v>1.068110737726023</v>
       </c>
       <c r="F4" t="n">
-        <v>7.743592024567654</v>
+        <v>1.258333703992244</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.3842257220451</v>
+        <v>5.749936679832329</v>
       </c>
       <c r="D5" t="n">
-        <v>33.7597034905988</v>
+        <v>5.485951817222304</v>
       </c>
       <c r="E5" t="n">
-        <v>6.572989155237063</v>
+        <v>1.068110737726023</v>
       </c>
       <c r="F5" t="n">
-        <v>7.743592024567654</v>
+        <v>1.258333703992244</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.97258240794484</v>
+        <v>4.545544641291037</v>
       </c>
       <c r="D6" t="n">
-        <v>27.74261105107568</v>
+        <v>4.508174295799798</v>
       </c>
       <c r="E6" t="n">
-        <v>6.572989155237063</v>
+        <v>1.068110737726023</v>
       </c>
       <c r="F6" t="n">
-        <v>7.743592024567654</v>
+        <v>1.258333703992244</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>39.51547238383925</v>
+        <v>6.421264262373878</v>
       </c>
       <c r="D7" t="n">
-        <v>39.21503975191738</v>
+        <v>6.372443959686574</v>
       </c>
       <c r="E7" t="n">
-        <v>6.572989155237063</v>
+        <v>1.068110737726023</v>
       </c>
       <c r="F7" t="n">
-        <v>7.743592024567654</v>
+        <v>1.258333703992244</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
